--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/45.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/45.xlsx
@@ -426,13 +426,13 @@
         <v>-9.245231405843283</v>
       </c>
       <c r="E2">
-        <v>-17.10451483650133</v>
+        <v>-21.09294567638696</v>
       </c>
       <c r="F2">
-        <v>1.605742846137374</v>
+        <v>1.13242365258657</v>
       </c>
       <c r="G2">
-        <v>-12.3134390395451</v>
+        <v>-13.61182169183893</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.621752052721062</v>
       </c>
       <c r="E3">
-        <v>-16.54909749946056</v>
+        <v>-20.28712636909206</v>
       </c>
       <c r="F3">
-        <v>1.744792598371299</v>
+        <v>1.355552696204645</v>
       </c>
       <c r="G3">
-        <v>-12.72676795694523</v>
+        <v>-13.57885854005275</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.873578121174788</v>
       </c>
       <c r="E4">
-        <v>-17.44531873337059</v>
+        <v>-19.62615030293249</v>
       </c>
       <c r="F4">
-        <v>1.791432996618523</v>
+        <v>1.904583013636518</v>
       </c>
       <c r="G4">
-        <v>-12.54618592842119</v>
+        <v>-12.78408761636717</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.055602490022943</v>
       </c>
       <c r="E5">
-        <v>-18.53694362071159</v>
+        <v>-20.37026915187289</v>
       </c>
       <c r="F5">
-        <v>1.850846820216914</v>
+        <v>1.287170967103546</v>
       </c>
       <c r="G5">
-        <v>-12.02380561249292</v>
+        <v>-13.86697768335525</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.177432811232205</v>
       </c>
       <c r="E6">
-        <v>-18.97214808674474</v>
+        <v>-21.30543526224888</v>
       </c>
       <c r="F6">
-        <v>1.77651906989852</v>
+        <v>2.170812013222251</v>
       </c>
       <c r="G6">
-        <v>-12.22144671190451</v>
+        <v>-13.22026039826416</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.265328994083485</v>
       </c>
       <c r="E7">
-        <v>-19.30117342272005</v>
+        <v>-22.10042245971743</v>
       </c>
       <c r="F7">
-        <v>1.622026892541607</v>
+        <v>2.089752949388709</v>
       </c>
       <c r="G7">
-        <v>-11.91846199432694</v>
+        <v>-12.09726231954421</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.344228804193837</v>
       </c>
       <c r="E8">
-        <v>-20.25788601242453</v>
+        <v>-22.42750508034345</v>
       </c>
       <c r="F8">
-        <v>2.109994935243517</v>
+        <v>1.87934928581244</v>
       </c>
       <c r="G8">
-        <v>-10.81485265380175</v>
+        <v>-12.47115095379981</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.442053230475546</v>
       </c>
       <c r="E9">
-        <v>-20.76146137902549</v>
+        <v>-25.26641449270001</v>
       </c>
       <c r="F9">
-        <v>1.657502554933899</v>
+        <v>1.916065842574125</v>
       </c>
       <c r="G9">
-        <v>-10.59529627559462</v>
+        <v>-11.7706232757446</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.581518822175615</v>
       </c>
       <c r="E10">
-        <v>-20.43558786095953</v>
+        <v>-24.15369597343128</v>
       </c>
       <c r="F10">
-        <v>1.562856608959638</v>
+        <v>2.351338121314348</v>
       </c>
       <c r="G10">
-        <v>-9.514950795925891</v>
+        <v>-11.1499342806738</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.787132814950484</v>
       </c>
       <c r="E11">
-        <v>-21.46033171568124</v>
+        <v>-24.28541116841838</v>
       </c>
       <c r="F11">
-        <v>1.414507604261886</v>
+        <v>2.393101092293888</v>
       </c>
       <c r="G11">
-        <v>-9.458697533510771</v>
+        <v>-13.61239262439028</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.079235086188872</v>
       </c>
       <c r="E12">
-        <v>-23.03591009174797</v>
+        <v>-26.67357892042147</v>
       </c>
       <c r="F12">
-        <v>1.032419826251003</v>
+        <v>2.105690738218571</v>
       </c>
       <c r="G12">
-        <v>-7.816800514937111</v>
+        <v>-10.49519276825908</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.4737164554137878</v>
       </c>
       <c r="E13">
-        <v>-24.55022274296492</v>
+        <v>-28.0614158210782</v>
       </c>
       <c r="F13">
-        <v>2.225858683873084</v>
+        <v>1.879801574414368</v>
       </c>
       <c r="G13">
-        <v>-8.370001344973252</v>
+        <v>-9.662284206388078</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.00895138226564237</v>
       </c>
       <c r="E14">
-        <v>-25.440575074561</v>
+        <v>-27.09037513961345</v>
       </c>
       <c r="F14">
-        <v>1.843403110735358</v>
+        <v>2.132168673881655</v>
       </c>
       <c r="G14">
-        <v>-7.942595987083103</v>
+        <v>-9.143575577384819</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.3581179368049999</v>
       </c>
       <c r="E15">
-        <v>-24.43285375363412</v>
+        <v>-29.69852257348714</v>
       </c>
       <c r="F15">
-        <v>2.02514691890957</v>
+        <v>2.486577383495395</v>
       </c>
       <c r="G15">
-        <v>-7.455275523517493</v>
+        <v>-8.654752314344984</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.5698618651592121</v>
       </c>
       <c r="E16">
-        <v>-26.14998769870661</v>
+        <v>-27.95728808974583</v>
       </c>
       <c r="F16">
-        <v>1.866216349008456</v>
+        <v>2.004081535856378</v>
       </c>
       <c r="G16">
-        <v>-5.986899344671947</v>
+        <v>-7.63149352736747</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.6478811214011768</v>
       </c>
       <c r="E17">
-        <v>-25.92352777053103</v>
+        <v>-30.33728421040208</v>
       </c>
       <c r="F17">
-        <v>1.892074665854246</v>
+        <v>2.427547922371902</v>
       </c>
       <c r="G17">
-        <v>-6.243687743914091</v>
+        <v>-8.659257431546102</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.599597566936121</v>
       </c>
       <c r="E18">
-        <v>-27.8411417883971</v>
+        <v>-30.89807684608995</v>
       </c>
       <c r="F18">
-        <v>2.62634615863495</v>
+        <v>3.194871274524307</v>
       </c>
       <c r="G18">
-        <v>-6.0616291656883</v>
+        <v>-8.265041629729735</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.4376739894958312</v>
       </c>
       <c r="E19">
-        <v>-26.92130909101108</v>
+        <v>-31.91611176656931</v>
       </c>
       <c r="F19">
-        <v>2.290312294750108</v>
+        <v>2.176481359727011</v>
       </c>
       <c r="G19">
-        <v>-5.479970301067095</v>
+        <v>-7.983614537797721</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.1736330833965908</v>
       </c>
       <c r="E20">
-        <v>-28.09753040128937</v>
+        <v>-29.10159724369207</v>
       </c>
       <c r="F20">
-        <v>2.276531574637136</v>
+        <v>2.764103657720508</v>
       </c>
       <c r="G20">
-        <v>-4.688359193743261</v>
+        <v>-6.391493650280837</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.1772182164373508</v>
       </c>
       <c r="E21">
-        <v>-28.41325560910415</v>
+        <v>-32.80807397067512</v>
       </c>
       <c r="F21">
-        <v>2.430755360955542</v>
+        <v>3.689398330321584</v>
       </c>
       <c r="G21">
-        <v>-5.647778534060217</v>
+        <v>-6.549080878116288</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.597968182002908</v>
       </c>
       <c r="E22">
-        <v>-29.31767790944206</v>
+        <v>-33.2065751548761</v>
       </c>
       <c r="F22">
-        <v>2.419217859769351</v>
+        <v>2.516327370399536</v>
       </c>
       <c r="G22">
-        <v>-3.632435846141475</v>
+        <v>-5.677319371759897</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.070505843789895</v>
       </c>
       <c r="E23">
-        <v>-29.77080607559758</v>
+        <v>-32.16364042006558</v>
       </c>
       <c r="F23">
-        <v>2.185094723981321</v>
+        <v>3.221910843286488</v>
       </c>
       <c r="G23">
-        <v>-3.696432791436885</v>
+        <v>-7.204081607034202</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.581080921115261</v>
       </c>
       <c r="E24">
-        <v>-30.97326762851331</v>
+        <v>-31.89611176111443</v>
       </c>
       <c r="F24">
-        <v>2.665029259610881</v>
+        <v>2.947875309296772</v>
       </c>
       <c r="G24">
-        <v>-4.319270986629121</v>
+        <v>-5.413102286907171</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.115661569235189</v>
       </c>
       <c r="E25">
-        <v>-30.39865409015403</v>
+        <v>-32.59235784708274</v>
       </c>
       <c r="F25">
-        <v>2.509655699337389</v>
+        <v>3.191738389006919</v>
       </c>
       <c r="G25">
-        <v>-3.270028206122366</v>
+        <v>-5.789596211080977</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.660777198972755</v>
       </c>
       <c r="E26">
-        <v>-31.63199983580208</v>
+        <v>-33.71462012532263</v>
       </c>
       <c r="F26">
-        <v>2.312025461112289</v>
+        <v>3.215317038760204</v>
       </c>
       <c r="G26">
-        <v>-2.550213507740741</v>
+        <v>-4.92596229052733</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.204024397457552</v>
       </c>
       <c r="E27">
-        <v>-30.86904706346378</v>
+        <v>-33.4277933743878</v>
       </c>
       <c r="F27">
-        <v>2.513862149008805</v>
+        <v>3.27140910907337</v>
       </c>
       <c r="G27">
-        <v>-3.155526698583983</v>
+        <v>-6.124402215342037</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.733197790262197</v>
       </c>
       <c r="E28">
-        <v>-30.69780734733774</v>
+        <v>-34.51147078984534</v>
       </c>
       <c r="F28">
-        <v>2.464759842840462</v>
+        <v>2.916445393299754</v>
       </c>
       <c r="G28">
-        <v>-2.153654913730931</v>
+        <v>-4.415679838488726</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.236832755812006</v>
       </c>
       <c r="E29">
-        <v>-30.61724126626727</v>
+        <v>-33.94813994447617</v>
       </c>
       <c r="F29">
-        <v>2.72411670645257</v>
+        <v>3.368145854372296</v>
       </c>
       <c r="G29">
-        <v>-1.857416387679584</v>
+        <v>-4.461059132655847</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.708624516748608</v>
       </c>
       <c r="E30">
-        <v>-29.03641891729967</v>
+        <v>-34.71526117713852</v>
       </c>
       <c r="F30">
-        <v>2.597099819111711</v>
+        <v>3.16187077393158</v>
       </c>
       <c r="G30">
-        <v>-3.300189194696782</v>
+        <v>-4.663999404885943</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.141738274243242</v>
       </c>
       <c r="E31">
-        <v>-31.21140422691767</v>
+        <v>-33.87517717126458</v>
       </c>
       <c r="F31">
-        <v>2.985254559980697</v>
+        <v>2.721141210741714</v>
       </c>
       <c r="G31">
-        <v>-1.864497263804865</v>
+        <v>-6.01737204929451</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.530238639454438</v>
       </c>
       <c r="E32">
-        <v>-30.68289508243048</v>
+        <v>-34.52888503664184</v>
       </c>
       <c r="F32">
-        <v>2.195873440626548</v>
+        <v>2.680276190026809</v>
       </c>
       <c r="G32">
-        <v>-2.481314417435521</v>
+        <v>-4.305109234378558</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.869111209822483</v>
       </c>
       <c r="E33">
-        <v>-30.37610228959583</v>
+        <v>-33.79012563668952</v>
       </c>
       <c r="F33">
-        <v>2.970955281873572</v>
+        <v>3.336276903651794</v>
       </c>
       <c r="G33">
-        <v>-2.515186467593669</v>
+        <v>-5.663616990527657</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.152481301001116</v>
       </c>
       <c r="E34">
-        <v>-30.68819339701945</v>
+        <v>-32.51912110119369</v>
       </c>
       <c r="F34">
-        <v>2.260290603337848</v>
+        <v>3.009649979993143</v>
       </c>
       <c r="G34">
-        <v>-2.650090610788678</v>
+        <v>-6.051329411213204</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.37559216400338</v>
       </c>
       <c r="E35">
-        <v>-29.19302260543292</v>
+        <v>-32.62661348871376</v>
       </c>
       <c r="F35">
-        <v>2.712890671409831</v>
+        <v>3.089564240076017</v>
       </c>
       <c r="G35">
-        <v>-3.745007995402905</v>
+        <v>-7.433399619380674</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.537477800050132</v>
       </c>
       <c r="E36">
-        <v>-28.46084081397675</v>
+        <v>-31.36158880314505</v>
       </c>
       <c r="F36">
-        <v>2.350698621679387</v>
+        <v>2.721732665067313</v>
       </c>
       <c r="G36">
-        <v>-3.327843329999782</v>
+        <v>-5.913544355489001</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.63651128678782</v>
       </c>
       <c r="E37">
-        <v>-29.11058626459729</v>
+        <v>-32.88054540445687</v>
       </c>
       <c r="F37">
-        <v>2.744184735152791</v>
+        <v>3.719524396026596</v>
       </c>
       <c r="G37">
-        <v>-3.171506247578479</v>
+        <v>-5.982709224740536</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.674437131291213</v>
       </c>
       <c r="E38">
-        <v>-27.32887628017542</v>
+        <v>-31.00636850927238</v>
       </c>
       <c r="F38">
-        <v>2.899443980724697</v>
+        <v>2.661840045110103</v>
       </c>
       <c r="G38">
-        <v>-5.076097864201283</v>
+        <v>-6.498743658172847</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.654559405108378</v>
       </c>
       <c r="E39">
-        <v>-28.66862078687069</v>
+        <v>-31.69293724628629</v>
       </c>
       <c r="F39">
-        <v>3.233188237108201</v>
+        <v>4.044973381238465</v>
       </c>
       <c r="G39">
-        <v>-4.583898224176778</v>
+        <v>-8.237065934713909</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.580826769121331</v>
       </c>
       <c r="E40">
-        <v>-25.7775659963158</v>
+        <v>-30.89255890051161</v>
       </c>
       <c r="F40">
-        <v>3.104194865144262</v>
+        <v>3.612086800618306</v>
       </c>
       <c r="G40">
-        <v>-4.665377517940909</v>
+        <v>-7.608292009720637</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.459301470106882</v>
       </c>
       <c r="E41">
-        <v>-27.8299836284422</v>
+        <v>-29.20700653316861</v>
       </c>
       <c r="F41">
-        <v>4.023102825069754</v>
+        <v>3.924011859612071</v>
       </c>
       <c r="G41">
-        <v>-5.807170433753363</v>
+        <v>-7.054385717049215</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.298170969198305</v>
       </c>
       <c r="E42">
-        <v>-25.5845669625829</v>
+        <v>-28.19659529868117</v>
       </c>
       <c r="F42">
-        <v>3.185550484508007</v>
+        <v>3.637516023149445</v>
       </c>
       <c r="G42">
-        <v>-6.212128954955351</v>
+        <v>-7.412248865208494</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.105138390109135</v>
       </c>
       <c r="E43">
-        <v>-24.46707996018409</v>
+        <v>-27.94951269987466</v>
       </c>
       <c r="F43">
-        <v>3.436086892015106</v>
+        <v>3.448437849990846</v>
       </c>
       <c r="G43">
-        <v>-7.228136242286491</v>
+        <v>-8.61163706305388</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.890260225888595</v>
       </c>
       <c r="E44">
-        <v>-24.36227295775057</v>
+        <v>-28.82027938138757</v>
       </c>
       <c r="F44">
-        <v>3.836930564760176</v>
+        <v>3.043349622673832</v>
       </c>
       <c r="G44">
-        <v>-5.882992901549011</v>
+        <v>-8.04182997070539</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.660387219528104</v>
       </c>
       <c r="E45">
-        <v>-23.8845506492594</v>
+        <v>-28.29039810927605</v>
       </c>
       <c r="F45">
-        <v>4.075285001241705</v>
+        <v>3.11987420334445</v>
       </c>
       <c r="G45">
-        <v>-7.372605146327283</v>
+        <v>-9.631066664471522</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.420181710993016</v>
       </c>
       <c r="E46">
-        <v>-24.40732221717887</v>
+        <v>-22.5502176690033</v>
       </c>
       <c r="F46">
-        <v>4.533082246398852</v>
+        <v>4.45475182479013</v>
       </c>
       <c r="G46">
-        <v>-6.980174329039254</v>
+        <v>-9.646793559405939</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.173764832063323</v>
       </c>
       <c r="E47">
-        <v>-23.43692457902321</v>
+        <v>-27.16062082842043</v>
       </c>
       <c r="F47">
-        <v>4.083245611982608</v>
+        <v>4.05842606785993</v>
       </c>
       <c r="G47">
-        <v>-5.470316947239209</v>
+        <v>-8.586276501620931</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.923886287183684</v>
       </c>
       <c r="E48">
-        <v>-21.60002608186986</v>
+        <v>-25.50205816616314</v>
       </c>
       <c r="F48">
-        <v>4.457704126213708</v>
+        <v>4.517740882099005</v>
       </c>
       <c r="G48">
-        <v>-8.147974206931867</v>
+        <v>-8.038860465194091</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.672672737961103</v>
       </c>
       <c r="E49">
-        <v>-22.19233689665112</v>
+        <v>-24.89602607513864</v>
       </c>
       <c r="F49">
-        <v>4.054444934122075</v>
+        <v>4.082897697673433</v>
       </c>
       <c r="G49">
-        <v>-6.884087036892475</v>
+        <v>-9.574032471325253</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.423817265851146</v>
       </c>
       <c r="E50">
-        <v>-21.81579881138734</v>
+        <v>-24.03053053737066</v>
       </c>
       <c r="F50">
-        <v>4.70275839824908</v>
+        <v>4.658861552839929</v>
       </c>
       <c r="G50">
-        <v>-7.972110575010308</v>
+        <v>-10.85380731615547</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.178160659461538</v>
       </c>
       <c r="E51">
-        <v>-20.23411605235827</v>
+        <v>-23.24789248852102</v>
       </c>
       <c r="F51">
-        <v>4.453429750415263</v>
+        <v>3.595598975832984</v>
       </c>
       <c r="G51">
-        <v>-8.173196957059318</v>
+        <v>-9.528699114259965</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.935507143419668</v>
       </c>
       <c r="E52">
-        <v>-19.57222976292316</v>
+        <v>-21.97666832203582</v>
       </c>
       <c r="F52">
-        <v>4.879051548912871</v>
+        <v>4.126259417740376</v>
       </c>
       <c r="G52">
-        <v>-7.878044515344147</v>
+        <v>-9.968376240782439</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.696630149694633</v>
       </c>
       <c r="E53">
-        <v>-18.30729564683461</v>
+        <v>-22.26840167455796</v>
       </c>
       <c r="F53">
-        <v>4.893821339704786</v>
+        <v>4.182545326025797</v>
       </c>
       <c r="G53">
-        <v>-7.762082864211811</v>
+        <v>-10.19762862869772</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.462031781194394</v>
       </c>
       <c r="E54">
-        <v>-17.73967860081718</v>
+        <v>-19.74523105543819</v>
       </c>
       <c r="F54">
-        <v>4.670503428318873</v>
+        <v>4.353245339985885</v>
       </c>
       <c r="G54">
-        <v>-8.449187064867331</v>
+        <v>-9.890765507236893</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.233781437642597</v>
       </c>
       <c r="E55">
-        <v>-17.61638636748434</v>
+        <v>-19.57304488824454</v>
       </c>
       <c r="F55">
-        <v>4.440889924671684</v>
+        <v>4.409774788287729</v>
       </c>
       <c r="G55">
-        <v>-7.46763916635348</v>
+        <v>-10.87179169152279</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.015708182374581</v>
       </c>
       <c r="E56">
-        <v>-17.9884231495845</v>
+        <v>-20.07215517947394</v>
       </c>
       <c r="F56">
-        <v>4.497238788879717</v>
+        <v>3.292616971319843</v>
       </c>
       <c r="G56">
-        <v>-8.585718693955826</v>
+        <v>-9.899460744369421</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.81007186198934</v>
       </c>
       <c r="E57">
-        <v>-16.14084651072107</v>
+        <v>-22.93020645146093</v>
       </c>
       <c r="F57">
-        <v>4.581168974131363</v>
+        <v>3.498065341092565</v>
       </c>
       <c r="G57">
-        <v>-9.395504487497426</v>
+        <v>-9.932033430790028</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.618652301387796</v>
       </c>
       <c r="E58">
-        <v>-16.15553688040195</v>
+        <v>-17.73398178051553</v>
       </c>
       <c r="F58">
-        <v>4.056661645291967</v>
+        <v>3.997315747820605</v>
       </c>
       <c r="G58">
-        <v>-7.726146925692772</v>
+        <v>-10.99825981408847</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.444120652376104</v>
       </c>
       <c r="E59">
-        <v>-16.98223698134622</v>
+        <v>-20.25384661360969</v>
       </c>
       <c r="F59">
-        <v>4.063286927779557</v>
+        <v>3.74209078081366</v>
       </c>
       <c r="G59">
-        <v>-9.337344835356268</v>
+        <v>-10.71510023717307</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.28840617207274</v>
       </c>
       <c r="E60">
-        <v>-16.1426986565902</v>
+        <v>-18.32181846297721</v>
       </c>
       <c r="F60">
-        <v>3.882086528621582</v>
+        <v>4.323336306540406</v>
       </c>
       <c r="G60">
-        <v>-9.806910609063722</v>
+        <v>-10.50833406060466</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.154513709413053</v>
       </c>
       <c r="E61">
-        <v>-14.64175406064389</v>
+        <v>-18.17222485260783</v>
       </c>
       <c r="F61">
-        <v>3.977380257904832</v>
+        <v>4.048638078628451</v>
       </c>
       <c r="G61">
-        <v>-8.599857477655474</v>
+        <v>-10.28824940572647</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.045510648204699</v>
       </c>
       <c r="E62">
-        <v>-14.09437929344075</v>
+        <v>-18.330549360864</v>
       </c>
       <c r="F62">
-        <v>4.313602989557512</v>
+        <v>3.852702680109478</v>
       </c>
       <c r="G62">
-        <v>-8.589026165287747</v>
+        <v>-9.858350319451137</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.962544566895655</v>
       </c>
       <c r="E63">
-        <v>-13.36894039978199</v>
+        <v>-15.32705708917266</v>
       </c>
       <c r="F63">
-        <v>4.316555290981089</v>
+        <v>3.063715863639061</v>
       </c>
       <c r="G63">
-        <v>-8.425014305638902</v>
+        <v>-10.47169265945034</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.904739240751505</v>
       </c>
       <c r="E64">
-        <v>-12.63335319587205</v>
+        <v>-17.21241478668209</v>
       </c>
       <c r="F64">
-        <v>4.031413006854637</v>
+        <v>4.127541730479909</v>
       </c>
       <c r="G64">
-        <v>-8.007347613337185</v>
+        <v>-10.37831893753322</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.87166092712109</v>
       </c>
       <c r="E65">
-        <v>-12.71683561420345</v>
+        <v>-17.0405003279289</v>
       </c>
       <c r="F65">
-        <v>3.968119110341533</v>
+        <v>3.690230011193994</v>
       </c>
       <c r="G65">
-        <v>-8.276791684134107</v>
+        <v>-9.89887340571028</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.861619779859669</v>
       </c>
       <c r="E66">
-        <v>-11.6188029361416</v>
+        <v>-16.94250415040292</v>
       </c>
       <c r="F66">
-        <v>3.67803478628998</v>
+        <v>3.52205817454725</v>
       </c>
       <c r="G66">
-        <v>-7.893528599883166</v>
+        <v>-9.528912393661329</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.873445968627532</v>
       </c>
       <c r="E67">
-        <v>-12.93433822079186</v>
+        <v>-16.53558906149568</v>
       </c>
       <c r="F67">
-        <v>3.813101748051245</v>
+        <v>3.214245131340982</v>
       </c>
       <c r="G67">
-        <v>-8.568006659977943</v>
+        <v>-10.77936952385791</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.905635720041319</v>
       </c>
       <c r="E68">
-        <v>-12.10949026571673</v>
+        <v>-15.52363361737163</v>
       </c>
       <c r="F68">
-        <v>3.759261180338888</v>
+        <v>2.933400417300254</v>
       </c>
       <c r="G68">
-        <v>-7.828901660048343</v>
+        <v>-10.27144298889899</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.955607086690443</v>
       </c>
       <c r="E69">
-        <v>-12.35732911968252</v>
+        <v>-15.40604726128846</v>
       </c>
       <c r="F69">
-        <v>3.351310115277799</v>
+        <v>3.169347618109248</v>
       </c>
       <c r="G69">
-        <v>-7.592962142594912</v>
+        <v>-10.5545205352754</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.019573818730479</v>
       </c>
       <c r="E70">
-        <v>-13.22187367790889</v>
+        <v>-16.2095887461575</v>
       </c>
       <c r="F70">
-        <v>3.250911986058499</v>
+        <v>3.454559485097535</v>
       </c>
       <c r="G70">
-        <v>-7.303473089291342</v>
+        <v>-7.692652216013961</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.095417906526097</v>
       </c>
       <c r="E71">
-        <v>-12.69501289796049</v>
+        <v>-15.35245277140768</v>
       </c>
       <c r="F71">
-        <v>2.581213389060822</v>
+        <v>2.771940013350991</v>
       </c>
       <c r="G71">
-        <v>-5.626978870594897</v>
+        <v>-8.156433196112115</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.180975634376663</v>
       </c>
       <c r="E72">
-        <v>-11.83988303719607</v>
+        <v>-15.29889450931896</v>
       </c>
       <c r="F72">
-        <v>3.022075491035135</v>
+        <v>2.663973919539715</v>
       </c>
       <c r="G72">
-        <v>-6.806105525310712</v>
+        <v>-11.00211524942082</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.27480231231486</v>
       </c>
       <c r="E73">
-        <v>-13.37930154831154</v>
+        <v>-16.04101177274796</v>
       </c>
       <c r="F73">
-        <v>3.02246151024484</v>
+        <v>3.448121413642977</v>
       </c>
       <c r="G73">
-        <v>-5.881391665428002</v>
+        <v>-9.678677189299064</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.375284396782929</v>
       </c>
       <c r="E74">
-        <v>-12.12357381988058</v>
+        <v>-16.40235682771601</v>
       </c>
       <c r="F74">
-        <v>3.163328700560507</v>
+        <v>3.02471632631526</v>
       </c>
       <c r="G74">
-        <v>-5.084553572159972</v>
+        <v>-8.880782542688893</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.480134096088131</v>
       </c>
       <c r="E75">
-        <v>-11.04534415865427</v>
+        <v>-15.69753154774017</v>
       </c>
       <c r="F75">
-        <v>2.620492914566769</v>
+        <v>2.380147082848909</v>
       </c>
       <c r="G75">
-        <v>-5.145538356063811</v>
+        <v>-9.196232620970788</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.585272414931049</v>
       </c>
       <c r="E76">
-        <v>-12.78230376293234</v>
+        <v>-14.48676250925737</v>
       </c>
       <c r="F76">
-        <v>2.38442311538216</v>
+        <v>2.382569229134694</v>
       </c>
       <c r="G76">
-        <v>-6.208686953539494</v>
+        <v>-8.561598434272348</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.688570853269598</v>
       </c>
       <c r="E77">
-        <v>-12.48367807297053</v>
+        <v>-16.31449537501919</v>
       </c>
       <c r="F77">
-        <v>2.025016036859927</v>
+        <v>2.20502027348826</v>
       </c>
       <c r="G77">
-        <v>-5.003067715952722</v>
+        <v>-7.081865947609565</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.787292536064311</v>
       </c>
       <c r="E78">
-        <v>-13.30480362241136</v>
+        <v>-16.20372437231757</v>
       </c>
       <c r="F78">
-        <v>2.46510278694522</v>
+        <v>2.299101272893811</v>
       </c>
       <c r="G78">
-        <v>-5.034268851761482</v>
+        <v>-8.369811034122804</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.879592946490888</v>
       </c>
       <c r="E79">
-        <v>-13.1016155221612</v>
+        <v>-16.82575103353716</v>
       </c>
       <c r="F79">
-        <v>2.124517872549399</v>
+        <v>2.930144933407252</v>
       </c>
       <c r="G79">
-        <v>-3.243335468736283</v>
+        <v>-9.427808113750158</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.963562877523492</v>
       </c>
       <c r="E80">
-        <v>-14.36654058130173</v>
+        <v>-15.9204185099237</v>
       </c>
       <c r="F80">
-        <v>2.161355370951892</v>
+        <v>2.313379013448463</v>
       </c>
       <c r="G80">
-        <v>-4.461564440776001</v>
+        <v>-6.90515247930411</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.037061062004752</v>
       </c>
       <c r="E81">
-        <v>-14.02536534956385</v>
+        <v>-17.36914980056157</v>
       </c>
       <c r="F81">
-        <v>2.407652194091464</v>
+        <v>1.772975314149344</v>
       </c>
       <c r="G81">
-        <v>-3.246859500691126</v>
+        <v>-7.87909122502161</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.096590911866899</v>
       </c>
       <c r="E82">
-        <v>-14.72197597768977</v>
+        <v>-16.89754546045477</v>
       </c>
       <c r="F82">
-        <v>1.463311698165222</v>
+        <v>2.108210631857887</v>
       </c>
       <c r="G82">
-        <v>-3.855506412638765</v>
+        <v>-6.815109197269829</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.14209569036471</v>
       </c>
       <c r="E83">
-        <v>-14.25199283127771</v>
+        <v>-18.32103956544789</v>
       </c>
       <c r="F83">
-        <v>2.235963109452432</v>
+        <v>2.151479574775716</v>
       </c>
       <c r="G83">
-        <v>-3.60433874592795</v>
+        <v>-7.359086513502371</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.173265044901728</v>
       </c>
       <c r="E84">
-        <v>-16.90230488663683</v>
+        <v>-17.28675421599201</v>
       </c>
       <c r="F84">
-        <v>1.927775644180099</v>
+        <v>1.951516653944333</v>
       </c>
       <c r="G84">
-        <v>-3.020428963316966</v>
+        <v>-6.886019676390988</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.192678871252484</v>
       </c>
       <c r="E85">
-        <v>-16.65964660693581</v>
+        <v>-19.30678420201555</v>
       </c>
       <c r="F85">
-        <v>1.480213706651943</v>
+        <v>2.567343205268347</v>
       </c>
       <c r="G85">
-        <v>-2.490741366975805</v>
+        <v>-6.716272241456235</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.204136581502629</v>
       </c>
       <c r="E86">
-        <v>-17.64506066490091</v>
+        <v>-20.43139902250243</v>
       </c>
       <c r="F86">
-        <v>1.446986233390849</v>
+        <v>1.238552427498437</v>
       </c>
       <c r="G86">
-        <v>-2.521765316820355</v>
+        <v>-6.356880044050255</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.212317191123879</v>
       </c>
       <c r="E87">
-        <v>-19.26276290618699</v>
+        <v>-23.07992233062851</v>
       </c>
       <c r="F87">
-        <v>1.583246044212145</v>
+        <v>2.181012529420324</v>
       </c>
       <c r="G87">
-        <v>-3.252030705868811</v>
+        <v>-6.552709909161035</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.220602645097733</v>
       </c>
       <c r="E88">
-        <v>-20.05726102846271</v>
+        <v>-23.628089580783</v>
       </c>
       <c r="F88">
-        <v>1.430094165312962</v>
+        <v>2.08201268437695</v>
       </c>
       <c r="G88">
-        <v>-2.478118507636621</v>
+        <v>-6.493992449354772</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.236259316482728</v>
       </c>
       <c r="E89">
-        <v>-21.8940644276619</v>
+        <v>-24.98157800609155</v>
       </c>
       <c r="F89">
-        <v>0.9361950120070067</v>
+        <v>1.339111259993881</v>
       </c>
       <c r="G89">
-        <v>-2.890466339790479</v>
+        <v>-5.904580058188598</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.264891068001523</v>
       </c>
       <c r="E90">
-        <v>-23.20124920624202</v>
+        <v>-26.07002843315318</v>
       </c>
       <c r="F90">
-        <v>0.2670166297382877</v>
+        <v>1.985544330116531</v>
       </c>
       <c r="G90">
-        <v>-2.513135704119016</v>
+        <v>-5.267694953500379</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.313764149923063</v>
       </c>
       <c r="E91">
-        <v>-23.55233273910869</v>
+        <v>-27.05641158455592</v>
       </c>
       <c r="F91">
-        <v>0.6220366744952942</v>
+        <v>1.686939418959782</v>
       </c>
       <c r="G91">
-        <v>-2.415571862270486</v>
+        <v>-5.316992026209476</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.388652648793765</v>
       </c>
       <c r="E92">
-        <v>-26.91220232978165</v>
+        <v>-28.85490409365022</v>
       </c>
       <c r="F92">
-        <v>0.8236546733974714</v>
+        <v>0.4148653005247491</v>
       </c>
       <c r="G92">
-        <v>-3.057618328471712</v>
+        <v>-5.633239441330318</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.493750300539678</v>
       </c>
       <c r="E93">
-        <v>-27.6008564290761</v>
+        <v>-29.73664553192071</v>
       </c>
       <c r="F93">
-        <v>0.726629656242371</v>
+        <v>0.8066847387837208</v>
       </c>
       <c r="G93">
-        <v>-2.477993821217363</v>
+        <v>-7.628816050574964</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.628675322565374</v>
       </c>
       <c r="E94">
-        <v>-29.34584954624378</v>
+        <v>-32.62761880994346</v>
       </c>
       <c r="F94">
-        <v>-0.0689625618979694</v>
+        <v>-0.1534137902459762</v>
       </c>
       <c r="G94">
-        <v>-1.872260634014511</v>
+        <v>-5.14915098100076</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.795934326198528</v>
       </c>
       <c r="E95">
-        <v>-31.94785410512607</v>
+        <v>-35.03613978837403</v>
       </c>
       <c r="F95">
-        <v>-0.06697365176384779</v>
+        <v>0.05023122369085147</v>
       </c>
       <c r="G95">
-        <v>-2.106848288185452</v>
+        <v>-5.907040974358182</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.995253523591813</v>
       </c>
       <c r="E96">
-        <v>-33.85851012267936</v>
+        <v>-35.54584218030737</v>
       </c>
       <c r="F96">
-        <v>-0.2657669178224787</v>
+        <v>-0.4284541338952876</v>
       </c>
       <c r="G96">
-        <v>-2.764631492985774</v>
+        <v>-5.452900223201676</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.222776572473502</v>
       </c>
       <c r="E97">
-        <v>-34.35087298763732</v>
+        <v>-37.88546921942224</v>
       </c>
       <c r="F97">
-        <v>-0.2762987809816717</v>
+        <v>-0.2179593499047109</v>
       </c>
       <c r="G97">
-        <v>-2.652843555677053</v>
+        <v>-7.22696156496821</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.478424315542155</v>
       </c>
       <c r="E98">
-        <v>-38.34701355452101</v>
+        <v>-38.98622803883671</v>
       </c>
       <c r="F98">
-        <v>-0.2924627141124984</v>
+        <v>-0.2917287805936181</v>
       </c>
       <c r="G98">
-        <v>-2.41619857558834</v>
+        <v>-6.920551252082585</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.748411495453829</v>
       </c>
       <c r="E99">
-        <v>-40.66323064725323</v>
+        <v>-41.23452028569088</v>
       </c>
       <c r="F99">
-        <v>-0.3084154135556113</v>
+        <v>-0.1698312038020596</v>
       </c>
       <c r="G99">
-        <v>-2.972710158177961</v>
+        <v>-7.339435277582856</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.032201068980845</v>
       </c>
       <c r="E100">
-        <v>-42.05897879200135</v>
+        <v>-44.59873268293721</v>
       </c>
       <c r="F100">
-        <v>-0.9099410300376947</v>
+        <v>0.04115231695616889</v>
       </c>
       <c r="G100">
-        <v>-3.620974539234335</v>
+        <v>-6.844394099687872</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.30545723414172</v>
       </c>
       <c r="E101">
-        <v>-43.85446665859157</v>
+        <v>-46.8769671999301</v>
       </c>
       <c r="F101">
-        <v>-1.194124064711704</v>
+        <v>-0.6103926084091571</v>
       </c>
       <c r="G101">
-        <v>-2.780853852375669</v>
+        <v>-8.138767099236064</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.585662336901613</v>
       </c>
       <c r="E102">
-        <v>-44.62338116696096</v>
+        <v>-49.65162322671033</v>
       </c>
       <c r="F102">
-        <v>-0.8644363234997094</v>
+        <v>0.02228293588779895</v>
       </c>
       <c r="G102">
-        <v>-4.739227971579331</v>
+        <v>-7.571509516039262</v>
       </c>
     </row>
   </sheetData>
